--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADFE30E-D9EE-4AB2-AEE1-AE04D567E233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3647F041-D49E-422F-94E1-8E2605107637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="3225" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TECNICI" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>EMAIL</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>maurizio.adoni@wingaming.it</t>
-  </si>
-  <si>
-    <t>riccardo.rosso@wingaming.it</t>
   </si>
   <si>
     <t>luca.arabeni@wingaming.it</t>
@@ -156,7 +153,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,6 +178,13 @@
     </font>
     <font>
       <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -224,14 +228,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -547,6 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}">
+  <sheetPr codeName="Foglio1"/>
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -563,10 +567,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -574,13 +578,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -588,13 +592,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -602,13 +606,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -619,38 +623,38 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -661,10 +665,10 @@
         <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -672,41 +676,41 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -715,13 +719,13 @@
     <hyperlink ref="B8" r:id="rId1" xr:uid="{BA7E3E07-04A7-4A82-A601-E295B1CEE7C1}"/>
     <hyperlink ref="B7" r:id="rId2" xr:uid="{674147B8-D281-4466-9000-74594D6F788F}"/>
     <hyperlink ref="B5" r:id="rId3" xr:uid="{15CE2FCE-848C-4F40-938D-BC3D0F9B48D6}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{7BDF5DF0-8F33-4196-B74B-EA653231617C}"/>
-    <hyperlink ref="B3" r:id="rId5" xr:uid="{020A4D5C-2FEA-481B-A48F-EDC38B735D82}"/>
-    <hyperlink ref="B2" r:id="rId6" xr:uid="{7327F9ED-3DE1-420C-95C5-F4752F415793}"/>
-    <hyperlink ref="B4" r:id="rId7" xr:uid="{A2FB9C8F-D68C-4361-8EE9-2F87DF12FC28}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{1673C42C-99AA-4CAA-B432-0B487EF9C761}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{C0D225AA-2C6D-48FE-9A33-D79620D3B330}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{7C9ECE65-2AAC-4A18-9316-CD5B131DAB66}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{020A4D5C-2FEA-481B-A48F-EDC38B735D82}"/>
+    <hyperlink ref="B2" r:id="rId5" xr:uid="{7327F9ED-3DE1-420C-95C5-F4752F415793}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{A2FB9C8F-D68C-4361-8EE9-2F87DF12FC28}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{1673C42C-99AA-4CAA-B432-0B487EF9C761}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{C0D225AA-2C6D-48FE-9A33-D79620D3B330}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{7C9ECE65-2AAC-4A18-9316-CD5B131DAB66}"/>
+    <hyperlink ref="B6" r:id="rId10" xr:uid="{CB0ED145-0174-42AE-B2F7-0393391640A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3647F041-D49E-422F-94E1-8E2605107637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517D74D6-594F-4C23-B56B-DACD15352633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>EMAIL</t>
   </si>
@@ -147,13 +147,16 @@
   </si>
   <si>
     <t>WinAle2026</t>
+  </si>
+  <si>
+    <t>riccardo.rosso@wingaming.it</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,13 +181,6 @@
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -228,13 +224,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -633,8 +628,8 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>24</v>

--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517D74D6-594F-4C23-B56B-DACD15352633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29FD069-27A5-4703-816D-879CDB56CD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>EMAIL</t>
   </si>
@@ -150,6 +150,15 @@
   </si>
   <si>
     <t>riccardo.rosso@wingaming.it</t>
+  </si>
+  <si>
+    <t>Tecnico Prova</t>
+  </si>
+  <si>
+    <t>wingamingsrl@gmail.com</t>
+  </si>
+  <si>
+    <t>WinTecn2026</t>
   </si>
 </sst>
 </file>
@@ -224,12 +233,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -546,7 +557,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}">
   <sheetPr codeName="Foglio1"/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -706,6 +717,20 @@
       </c>
       <c r="D11" s="3" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -721,6 +746,7 @@
     <hyperlink ref="B10" r:id="rId8" xr:uid="{C0D225AA-2C6D-48FE-9A33-D79620D3B330}"/>
     <hyperlink ref="B11" r:id="rId9" xr:uid="{7C9ECE65-2AAC-4A18-9316-CD5B131DAB66}"/>
     <hyperlink ref="B6" r:id="rId10" xr:uid="{CB0ED145-0174-42AE-B2F7-0393391640A1}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{D7086F26-0731-4FFF-812B-B9C2337FBD3B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29FD069-27A5-4703-816D-879CDB56CD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86558EF4-8B11-4531-B2AA-A08B190DDFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,7 @@
     <t>wingamingsrl@gmail.com</t>
   </si>
   <si>
-    <t>WinTecn2026</t>
+    <t>WinTec2026</t>
   </si>
 </sst>
 </file>
@@ -233,14 +233,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -720,16 +718,16 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>30</v>
       </c>
     </row>

--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86558EF4-8B11-4531-B2AA-A08B190DDFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B34143-FBAF-491A-92DF-26B3E1E06759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -155,10 +155,10 @@
     <t>Tecnico Prova</t>
   </si>
   <si>
-    <t>wingamingsrl@gmail.com</t>
-  </si>
-  <si>
     <t>WinTec2026</t>
+  </si>
+  <si>
+    <t>arigoni.manuela@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -722,10 +722,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>30</v>

--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B34143-FBAF-491A-92DF-26B3E1E06759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C5E49F-8AB6-45F1-A187-E0DCDC476CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="TECNICI" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TECNICI!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TECNICI!$A$1:$D$12</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -691,13 +691,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -705,34 +705,34 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D11" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}"/>
+  <autoFilter ref="A1:D12" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}"/>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{BA7E3E07-04A7-4A82-A601-E295B1CEE7C1}"/>
     <hyperlink ref="B7" r:id="rId2" xr:uid="{674147B8-D281-4466-9000-74594D6F788F}"/>
@@ -741,10 +741,10 @@
     <hyperlink ref="B2" r:id="rId5" xr:uid="{7327F9ED-3DE1-420C-95C5-F4752F415793}"/>
     <hyperlink ref="B4" r:id="rId6" xr:uid="{A2FB9C8F-D68C-4361-8EE9-2F87DF12FC28}"/>
     <hyperlink ref="B9" r:id="rId7" xr:uid="{1673C42C-99AA-4CAA-B432-0B487EF9C761}"/>
-    <hyperlink ref="B10" r:id="rId8" xr:uid="{C0D225AA-2C6D-48FE-9A33-D79620D3B330}"/>
-    <hyperlink ref="B11" r:id="rId9" xr:uid="{7C9ECE65-2AAC-4A18-9316-CD5B131DAB66}"/>
+    <hyperlink ref="B11" r:id="rId8" xr:uid="{C0D225AA-2C6D-48FE-9A33-D79620D3B330}"/>
+    <hyperlink ref="B12" r:id="rId9" xr:uid="{7C9ECE65-2AAC-4A18-9316-CD5B131DAB66}"/>
     <hyperlink ref="B6" r:id="rId10" xr:uid="{CB0ED145-0174-42AE-B2F7-0393391640A1}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{D7086F26-0731-4FFF-812B-B9C2337FBD3B}"/>
+    <hyperlink ref="B10" r:id="rId11" xr:uid="{D7086F26-0731-4FFF-812B-B9C2337FBD3B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
